--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N102_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N102_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.69307390896907</v>
+        <v>4.175124510207474</v>
       </c>
       <c r="D2" t="n">
-        <v>26.08012308614375</v>
+        <v>4.238020001498359</v>
       </c>
       <c r="E2" t="n">
-        <v>9.270575523322256</v>
+        <v>1.506468522539867</v>
       </c>
       <c r="F2" t="n">
-        <v>8.498359789713312</v>
+        <v>1.380983465828413</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81286245892554</v>
+        <v>4.3570901495754</v>
       </c>
       <c r="D3" t="n">
-        <v>26.99125391343525</v>
+        <v>4.386078760933229</v>
       </c>
       <c r="E3" t="n">
-        <v>9.270575523322256</v>
+        <v>1.506468522539867</v>
       </c>
       <c r="F3" t="n">
-        <v>8.498359789713312</v>
+        <v>1.380983465828413</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.98133128210173</v>
+        <v>7.309466333341531</v>
       </c>
       <c r="D4" t="n">
-        <v>43.20228411554129</v>
+        <v>7.020371168775459</v>
       </c>
       <c r="E4" t="n">
-        <v>9.270575523322256</v>
+        <v>1.506468522539867</v>
       </c>
       <c r="F4" t="n">
-        <v>8.498359789713312</v>
+        <v>1.380983465828413</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.42303570497747</v>
+        <v>3.318743302058839</v>
       </c>
       <c r="D5" t="n">
-        <v>20.35581579182612</v>
+        <v>3.307820066171744</v>
       </c>
       <c r="E5" t="n">
-        <v>9.270575523322256</v>
+        <v>1.506468522539867</v>
       </c>
       <c r="F5" t="n">
-        <v>8.498359789713312</v>
+        <v>1.380983465828413</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
